--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_desktop_navigation.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_desktop_navigation.xlsx
@@ -468,7 +468,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>13</v>
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
